--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf318c89791eb4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2334c2aa87c04a62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R631ffeab07af46b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec930af49f974acb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2334c2aa87c04a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68fa6f37e53f4023"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec930af49f974acb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R441a8314442a421b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68fa6f37e53f4023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8184e531452f40fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R441a8314442a421b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf457542d61b94f62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8184e531452f40fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04dd7d9ae6ca44f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf457542d61b94f62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff3572c1270f4e85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04dd7d9ae6ca44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R313a5f600be64503"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff3572c1270f4e85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27603b9b21af42ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R313a5f600be64503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R506f8b72466d4fae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27603b9b21af42ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fed547cbdc14b64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R506f8b72466d4fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2fa380caf744bd1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fed547cbdc14b64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf323b0821224a35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra2fa380caf744bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R243fc96f243f4c53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf323b0821224a35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba06f322e02f4a13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R243fc96f243f4c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01d61f0a58164e9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba06f322e02f4a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf461e3340154760"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01d61f0a58164e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5040a7a29e544741"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf461e3340154760"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03f30e4c37444177"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5040a7a29e544741"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd573d404a4864c44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03f30e4c37444177"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R080cfe79b9d846a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd573d404a4864c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5801e8996d8d42e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R080cfe79b9d846a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04fc127c67ec41ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5801e8996d8d42e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R760bc12289694d05"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04fc127c67ec41ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf2bd382e77d4abb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R760bc12289694d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R761262eb698a4be1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf2bd382e77d4abb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b84c1657e94ea1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R761262eb698a4be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6927496dc407444f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b84c1657e94ea1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e11d69f67eb44b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>